--- a/EXCEL/Data/løn_data/Løn_klassificering_1000kr.xlsx
+++ b/EXCEL/Data/løn_data/Løn_klassificering_1000kr.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="58">
   <si>
     <t xml:space="preserve">Lønniveau - feb 2025 </t>
   </si>
@@ -46,9 +46,6 @@
     <t>Bruttoløn</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ialt</t>
-  </si>
-  <si>
     <t>Ergo- Fysio- og Jordemødre, basis Reg.</t>
   </si>
   <si>
@@ -100,7 +97,7 @@
     <t>Datasæt 02 2025</t>
   </si>
   <si>
-    <t>Kørsel 10.4.2026 10.53.13</t>
+    <t>Kørsel 14.4.2026 12.28.05</t>
   </si>
   <si>
     <t/>
@@ -636,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -700,83 +697,83 @@
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5">
-        <v>1495.4829258879693</v>
+        <v>7.437799999999999</v>
       </c>
       <c r="F3" s="6">
-        <v>23948.385324365587</v>
+        <v>337.09804</v>
       </c>
       <c r="G3" s="6">
-        <v>659.9772132448305</v>
+        <v>0</v>
       </c>
       <c r="H3" s="6">
-        <v>236.9007054387855</v>
+        <v>0</v>
       </c>
       <c r="I3" s="6">
-        <v>65134.454741153306</v>
+        <v>337.09804</v>
       </c>
       <c r="J3" s="6">
-        <v>79451.00693735122</v>
+        <v>403.5373713788428</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E4" s="8">
-        <v>372.99444099981685</v>
+        <v>6.2973</v>
       </c>
       <c r="F4" s="9">
-        <v>3983.3422411597685</v>
+        <v>288.24696</v>
       </c>
       <c r="G4" s="9">
-        <v>93.33315085365055</v>
+        <v>0</v>
       </c>
       <c r="H4" s="9">
-        <v>34.29819641483665</v>
+        <v>0</v>
       </c>
       <c r="I4" s="9">
-        <v>15543.372580794452</v>
+        <v>288.24696</v>
       </c>
       <c r="J4" s="9">
-        <v>18939.42422295831</v>
+        <v>346.352571611625</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5" s="5">
-        <v>53.6701</v>
+        <v>19.175600000000003</v>
       </c>
       <c r="F5" s="6">
-        <v>2131.1061500000005</v>
+        <v>794.1372700000001</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
@@ -785,30 +782,30 @@
         <v>0</v>
       </c>
       <c r="I5" s="6">
-        <v>2366.3075500000004</v>
+        <v>843.01926</v>
       </c>
       <c r="J5" s="6">
-        <v>2834.672838202324</v>
+        <v>1010.1517395803539</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
       <c r="E6" s="8">
-        <v>14.7351</v>
+        <v>7.1108</v>
       </c>
       <c r="F6" s="9">
-        <v>625.345</v>
+        <v>338.74776</v>
       </c>
       <c r="G6" s="9">
         <v>0</v>
@@ -817,94 +814,94 @@
         <v>0</v>
       </c>
       <c r="I6" s="9">
-        <v>665.3568799999999</v>
+        <v>338.74776</v>
       </c>
       <c r="J6" s="9">
-        <v>797.8021088241705</v>
+        <v>405.55113593956713</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E7" s="5">
-        <v>7.437799999999999</v>
+        <v>18.15092981908921</v>
       </c>
       <c r="F7" s="6">
-        <v>337.09804</v>
+        <v>108.76261421229187</v>
       </c>
       <c r="G7" s="6">
-        <v>0</v>
+        <v>14.424951084229946</v>
       </c>
       <c r="H7" s="6">
-        <v>0</v>
+        <v>9.090872323465348</v>
       </c>
       <c r="I7" s="6">
-        <v>337.09804</v>
+        <v>722.807065303479</v>
       </c>
       <c r="J7" s="6">
-        <v>403.53737137884275</v>
+        <v>893.5814093806289</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>14</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E8" s="8">
-        <v>6.2973</v>
+        <v>10.985476606363068</v>
       </c>
       <c r="F8" s="9">
-        <v>288.24695999999994</v>
+        <v>39.29021517155334</v>
       </c>
       <c r="G8" s="9">
-        <v>0</v>
+        <v>3.834500826126337</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
       </c>
       <c r="I8" s="9">
-        <v>288.24695999999994</v>
+        <v>418.1564738836712</v>
       </c>
       <c r="J8" s="9">
-        <v>346.35257161162514</v>
+        <v>512.4500812569953</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E9" s="5">
-        <v>27.824200000000005</v>
+        <v>12.2027</v>
       </c>
       <c r="F9" s="6">
-        <v>1040.2467900000001</v>
+        <v>87.53535000000001</v>
       </c>
       <c r="G9" s="6">
         <v>0</v>
@@ -913,30 +910,30 @@
         <v>0</v>
       </c>
       <c r="I9" s="6">
-        <v>1195.02046</v>
+        <v>522.6494015658334</v>
       </c>
       <c r="J9" s="6">
-        <v>1432.7835064544286</v>
+        <v>635.2796110633992</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E10" s="8">
-        <v>19.175600000000003</v>
+        <v>12.8108</v>
       </c>
       <c r="F10" s="9">
-        <v>794.1372700000001</v>
+        <v>53.222899999999996</v>
       </c>
       <c r="G10" s="9">
         <v>0</v>
@@ -945,30 +942,30 @@
         <v>0</v>
       </c>
       <c r="I10" s="9">
-        <v>843.01926</v>
+        <v>519.3810897791667</v>
       </c>
       <c r="J10" s="9">
-        <v>1010.1517395803542</v>
+        <v>631.3886937094185</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="5">
-        <v>11.1108</v>
+        <v>58.33860220525407</v>
       </c>
       <c r="F11" s="6">
-        <v>465.51436</v>
+        <v>309.92975814478666</v>
       </c>
       <c r="G11" s="6">
         <v>0</v>
@@ -977,254 +974,254 @@
         <v>0</v>
       </c>
       <c r="I11" s="6">
-        <v>505.93021</v>
+        <v>2394.3838186295816</v>
       </c>
       <c r="J11" s="6">
-        <v>604.0872229237239</v>
+        <v>2908.657074638256</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E12" s="8">
-        <v>7.1108</v>
+        <v>34.449851606363076</v>
       </c>
       <c r="F12" s="9">
-        <v>338.74776</v>
+        <v>141.4935694323144</v>
       </c>
       <c r="G12" s="9">
-        <v>0</v>
+        <v>0.21082685815215113</v>
       </c>
       <c r="H12" s="9">
-        <v>0</v>
+        <v>3.974304567170143</v>
       </c>
       <c r="I12" s="9">
-        <v>338.74776</v>
+        <v>1363.6454087886605</v>
       </c>
       <c r="J12" s="9">
-        <v>405.5511359395671</v>
+        <v>1657.7353626662507</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E13" s="5">
-        <v>319.32434099981685</v>
+        <v>86.89151285090456</v>
       </c>
       <c r="F13" s="6">
-        <v>1852.2360911597737</v>
+        <v>497.29559447910185</v>
       </c>
       <c r="G13" s="6">
-        <v>93.33315085365055</v>
+        <v>7.049141872706413</v>
       </c>
       <c r="H13" s="6">
-        <v>34.29819641483665</v>
+        <v>0</v>
       </c>
       <c r="I13" s="6">
-        <v>13177.065030794447</v>
+        <v>3582.163532800045</v>
       </c>
       <c r="J13" s="6">
-        <v>16104.75138475599</v>
+        <v>4352.2840300095</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E14" s="8">
-        <v>47.66610642545228</v>
+        <v>15.400000000000002</v>
       </c>
       <c r="F14" s="9">
-        <v>278.52368938384524</v>
+        <v>96.97916000000001</v>
       </c>
       <c r="G14" s="9">
-        <v>18.644586571173665</v>
+        <v>0</v>
       </c>
       <c r="H14" s="9">
-        <v>9.090872323465348</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9">
-        <v>1933.4969669567333</v>
+        <v>641.7622595833333</v>
       </c>
       <c r="J14" s="9">
-        <v>2369.0606801048534</v>
+        <v>779.3036101950516</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E15" s="5">
-        <v>18.150929819089207</v>
+        <v>9.4055</v>
       </c>
       <c r="F15" s="6">
-        <v>108.76261421229188</v>
+        <v>55.00761000000001</v>
       </c>
       <c r="G15" s="6">
-        <v>14.424951084229946</v>
+        <v>3.636013097075224</v>
       </c>
       <c r="H15" s="6">
-        <v>9.090872323465348</v>
+        <v>0</v>
       </c>
       <c r="I15" s="6">
-        <v>722.807065303479</v>
+        <v>380.8740500139168</v>
       </c>
       <c r="J15" s="6">
-        <v>893.581409380629</v>
+        <v>467.03575918066093</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E16" s="8">
-        <v>10.985476606363068</v>
+        <v>19.844444143907978</v>
       </c>
       <c r="F16" s="9">
-        <v>39.290215171553335</v>
+        <v>148.78696485258988</v>
       </c>
       <c r="G16" s="9">
-        <v>3.834500826126337</v>
+        <v>27.88434094137788</v>
       </c>
       <c r="H16" s="9">
-        <v>0</v>
+        <v>7.835671978169679</v>
       </c>
       <c r="I16" s="9">
-        <v>418.1564738836713</v>
+        <v>841.3588016072648</v>
       </c>
       <c r="J16" s="9">
-        <v>512.4500812569953</v>
+        <v>1052.8058526101006</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="E17" s="5">
-        <v>12.2027</v>
+        <v>20.922266063630694</v>
       </c>
       <c r="F17" s="6">
-        <v>87.53535000000001</v>
+        <v>168.19880507239392</v>
       </c>
       <c r="G17" s="6">
-        <v>0</v>
+        <v>3.066506497565508</v>
       </c>
       <c r="H17" s="6">
-        <v>0</v>
+        <v>3.586548247667551</v>
       </c>
       <c r="I17" s="6">
-        <v>522.6494015658334</v>
+        <v>929.1645900184066</v>
       </c>
       <c r="J17" s="6">
-        <v>635.2796110633992</v>
+        <v>1132.5509154070505</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E18" s="8">
-        <v>210.14746666252165</v>
+        <v>6.9189</v>
       </c>
       <c r="F18" s="9">
-        <v>1130.401752056203</v>
+        <v>46.309870000000004</v>
       </c>
       <c r="G18" s="9">
-        <v>7.2599687308585645</v>
+        <v>22.72753830757499</v>
       </c>
       <c r="H18" s="9">
-        <v>3.974304567170143</v>
+        <v>9.810799298363923</v>
       </c>
       <c r="I18" s="9">
-        <v>8617.094789129947</v>
+        <v>289.8083459608334</v>
       </c>
       <c r="J18" s="9">
-        <v>10470.234781951203</v>
+        <v>376.3700735028467</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="C19" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5">
-        <v>12.8108</v>
+        <v>19.040499999999998</v>
       </c>
       <c r="F19" s="6">
-        <v>53.222899999999996</v>
+        <v>793.1228</v>
       </c>
       <c r="G19" s="6">
         <v>0</v>
@@ -1233,996 +1230,516 @@
         <v>0</v>
       </c>
       <c r="I19" s="6">
-        <v>519.3810897791667</v>
+        <v>794.29462</v>
       </c>
       <c r="J19" s="6">
-        <v>631.3886937094184</v>
+        <v>970.311466809563</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="C20" s="7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="8">
-        <v>58.33860220525406</v>
+        <v>59.36769794135994</v>
       </c>
       <c r="F20" s="9">
-        <v>309.9297581447866</v>
+        <v>2565.8373425445843</v>
       </c>
       <c r="G20" s="9">
-        <v>0</v>
+        <v>52.356528104156254</v>
       </c>
       <c r="H20" s="9">
-        <v>0</v>
+        <v>8.930344478847982</v>
       </c>
       <c r="I20" s="9">
-        <v>2394.3838186295825</v>
+        <v>2575.800573857748</v>
       </c>
       <c r="J20" s="9">
-        <v>2908.657074638255</v>
+        <v>3100.285310123076</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="C21" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E21" s="5">
-        <v>34.449851606363076</v>
+        <v>109.70299999999999</v>
       </c>
       <c r="F21" s="6">
-        <v>141.49356943231442</v>
+        <v>5381.769699999998</v>
       </c>
       <c r="G21" s="6">
-        <v>0.21082685815215113</v>
+        <v>45.48366569477916</v>
       </c>
       <c r="H21" s="6">
-        <v>3.974304567170143</v>
+        <v>6.213504416747093</v>
       </c>
       <c r="I21" s="6">
-        <v>1363.6454087886605</v>
+        <v>5376.364529999998</v>
       </c>
       <c r="J21" s="6">
-        <v>1657.7353626662507</v>
+        <v>6471.965488129403</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="C22" s="7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="8">
-        <v>86.89151285090456</v>
+        <v>94.3649</v>
       </c>
       <c r="F22" s="9">
-        <v>497.29559447910174</v>
+        <v>4372.121229999999</v>
       </c>
       <c r="G22" s="9">
-        <v>7.0491418727064135</v>
+        <v>12.745410364142657</v>
       </c>
       <c r="H22" s="9">
-        <v>0</v>
+        <v>0.3651363883674145</v>
       </c>
       <c r="I22" s="9">
-        <v>3582.1635328000443</v>
+        <v>4372.707139999999</v>
       </c>
       <c r="J22" s="9">
-        <v>4352.2840300094995</v>
+        <v>5154.273443143156</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E23" s="5">
-        <v>15.4</v>
+        <v>46.34384273237679</v>
       </c>
       <c r="F23" s="6">
-        <v>96.97916000000001</v>
+        <v>296.2694665195057</v>
       </c>
       <c r="G23" s="6">
-        <v>0</v>
+        <v>2.5699188427257535</v>
       </c>
       <c r="H23" s="6">
-        <v>0</v>
+        <v>0.49201600209116936</v>
       </c>
       <c r="I23" s="6">
-        <v>641.7622595833334</v>
+        <v>1957.7480422965202</v>
       </c>
       <c r="J23" s="6">
-        <v>779.3036101950518</v>
+        <v>2390.289526592511</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>11</v>
-      </c>
       <c r="E24" s="8">
-        <v>61.5107679118431</v>
+        <v>183.92559950043002</v>
       </c>
       <c r="F24" s="9">
-        <v>443.3106497197245</v>
+        <v>1127.403517350456</v>
       </c>
       <c r="G24" s="9">
-        <v>67.42859555161834</v>
+        <v>58.13689550622582</v>
       </c>
       <c r="H24" s="9">
-        <v>21.233019524201154</v>
+        <v>1.099287486628294</v>
       </c>
       <c r="I24" s="9">
-        <v>2626.473274707772</v>
+        <v>7663.744349449863</v>
       </c>
       <c r="J24" s="9">
-        <v>3265.455922699927</v>
+        <v>9380.321964792774</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="5">
-        <v>9.405500000000002</v>
+        <v>179.84211107709115</v>
       </c>
       <c r="F25" s="6">
-        <v>55.00761</v>
+        <v>1335.5017075675999</v>
       </c>
       <c r="G25" s="6">
-        <v>3.636013097075224</v>
+        <v>156.72455452955484</v>
       </c>
       <c r="H25" s="6">
-        <v>0</v>
+        <v>79.62527758632659</v>
       </c>
       <c r="I25" s="6">
-        <v>380.87405001391676</v>
+        <v>7668.020237712357</v>
       </c>
       <c r="J25" s="6">
-        <v>467.0357591806609</v>
+        <v>9482.918798391334</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E26" s="8">
-        <v>19.844444143907978</v>
+        <v>339.6440762657325</v>
       </c>
       <c r="F26" s="9">
-        <v>148.78696485258982</v>
+        <v>3249.764161553251</v>
       </c>
       <c r="G26" s="9">
-        <v>27.884340941377882</v>
+        <v>174.76244378111005</v>
       </c>
       <c r="H26" s="9">
-        <v>7.835671978169679</v>
+        <v>83.80441819655418</v>
       </c>
       <c r="I26" s="9">
-        <v>841.3588016072648</v>
+        <v>15176.093084901426</v>
       </c>
       <c r="J26" s="9">
-        <v>1052.805852610101</v>
+        <v>18624.720937398157</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E27" s="5">
-        <v>20.92226606363069</v>
+        <v>87.4926467036613</v>
       </c>
       <c r="F27" s="6">
-        <v>168.19880507239404</v>
+        <v>816.0272387932642</v>
       </c>
       <c r="G27" s="6">
-        <v>3.066506497565508</v>
+        <v>63.76118755012273</v>
       </c>
       <c r="H27" s="6">
-        <v>3.586548247667551</v>
+        <v>18.92036989823699</v>
       </c>
       <c r="I27" s="6">
-        <v>929.1645900184064</v>
+        <v>3886.263211448923</v>
       </c>
       <c r="J27" s="6">
-        <v>1132.5509154070505</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="8">
-        <v>6.9189</v>
-      </c>
-      <c r="F28" s="9">
-        <v>46.30987</v>
-      </c>
-      <c r="G28" s="9">
-        <v>22.72753830757499</v>
-      </c>
-      <c r="H28" s="9">
-        <v>9.810799298363923</v>
-      </c>
-      <c r="I28" s="9">
-        <v>289.8083459608334</v>
-      </c>
-      <c r="J28" s="9">
-        <v>376.3700735028467</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="5">
-        <v>1122.4884848881516</v>
-      </c>
-      <c r="F29" s="6">
-        <v>19965.043083205837</v>
-      </c>
-      <c r="G29" s="6">
-        <v>566.6440623911802</v>
-      </c>
-      <c r="H29" s="6">
-        <v>202.60250902394887</v>
-      </c>
-      <c r="I29" s="6">
-        <v>49591.08216035889</v>
-      </c>
-      <c r="J29" s="6">
-        <v>60511.58271439321</v>
+        <v>4790.395001894331</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="8">
-        <v>282.47609794135997</v>
-      </c>
-      <c r="F30" s="9">
-        <v>13112.851072544592</v>
-      </c>
-      <c r="G30" s="9">
-        <v>110.5856041630781</v>
-      </c>
-      <c r="H30" s="9">
-        <v>15.50898528396249</v>
-      </c>
-      <c r="I30" s="9">
-        <v>13119.166863857752</v>
-      </c>
-      <c r="J30" s="9">
-        <v>15696.835708205197</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="A30" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="5">
-        <v>282.47609794135997</v>
-      </c>
-      <c r="F31" s="6">
-        <v>13112.851072544592</v>
-      </c>
-      <c r="G31" s="6">
-        <v>110.5856041630781</v>
-      </c>
-      <c r="H31" s="6">
-        <v>15.50898528396249</v>
-      </c>
-      <c r="I31" s="6">
-        <v>13119.166863857752</v>
-      </c>
-      <c r="J31" s="6">
-        <v>15696.835708205197</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="8">
-        <v>19.040499999999998</v>
-      </c>
-      <c r="F32" s="9">
-        <v>793.1228000000001</v>
-      </c>
-      <c r="G32" s="9">
-        <v>0</v>
-      </c>
-      <c r="H32" s="9">
-        <v>0</v>
-      </c>
-      <c r="I32" s="9">
-        <v>794.2946200000001</v>
-      </c>
-      <c r="J32" s="9">
-        <v>970.3114668095628</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="5">
-        <v>59.36769794135995</v>
-      </c>
-      <c r="F33" s="6">
-        <v>2565.837342544585</v>
-      </c>
-      <c r="G33" s="6">
-        <v>52.356528104156254</v>
-      </c>
-      <c r="H33" s="6">
-        <v>8.930344478847982</v>
-      </c>
-      <c r="I33" s="6">
-        <v>2575.800573857748</v>
-      </c>
-      <c r="J33" s="6">
-        <v>3100.2853101230776</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="8">
-        <v>109.703</v>
-      </c>
-      <c r="F34" s="9">
-        <v>5381.769699999999</v>
-      </c>
-      <c r="G34" s="9">
-        <v>45.483665694779155</v>
-      </c>
-      <c r="H34" s="9">
-        <v>6.213504416747093</v>
-      </c>
-      <c r="I34" s="9">
-        <v>5376.364529999999</v>
-      </c>
-      <c r="J34" s="9">
-        <v>6471.965488129405</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="5">
-        <v>94.3649</v>
-      </c>
-      <c r="F35" s="6">
-        <v>4372.121229999997</v>
-      </c>
-      <c r="G35" s="6">
-        <v>12.745410364142657</v>
-      </c>
-      <c r="H35" s="6">
-        <v>0.3651363883674145</v>
-      </c>
-      <c r="I35" s="6">
-        <v>4372.707139999997</v>
-      </c>
-      <c r="J35" s="6">
-        <v>5154.273443143158</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="8">
-        <v>840.0123869467905</v>
-      </c>
-      <c r="F36" s="9">
-        <v>6852.19201066117</v>
-      </c>
-      <c r="G36" s="9">
-        <v>456.0584582281019</v>
-      </c>
-      <c r="H36" s="9">
-        <v>187.09352373998635</v>
-      </c>
-      <c r="I36" s="9">
-        <v>36471.9152965012</v>
-      </c>
-      <c r="J36" s="9">
-        <v>44814.74700618788</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="5">
-        <v>840.0123869467905</v>
-      </c>
-      <c r="F37" s="6">
-        <v>6852.19201066117</v>
-      </c>
-      <c r="G37" s="6">
-        <v>456.0584582281019</v>
-      </c>
-      <c r="H37" s="6">
-        <v>187.09352373998635</v>
-      </c>
-      <c r="I37" s="6">
-        <v>36471.9152965012</v>
-      </c>
-      <c r="J37" s="6">
-        <v>44814.74700618788</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="8">
-        <v>46.34384273237679</v>
-      </c>
-      <c r="F38" s="9">
-        <v>296.26946651950584</v>
-      </c>
-      <c r="G38" s="9">
-        <v>2.5699188427257535</v>
-      </c>
-      <c r="H38" s="9">
-        <v>0.49201600209116936</v>
-      </c>
-      <c r="I38" s="9">
-        <v>1957.7480422965205</v>
-      </c>
-      <c r="J38" s="9">
-        <v>2390.289526592511</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="5">
-        <v>183.92559950043002</v>
-      </c>
-      <c r="F39" s="6">
-        <v>1127.4035173504553</v>
-      </c>
-      <c r="G39" s="6">
-        <v>58.136895506225834</v>
-      </c>
-      <c r="H39" s="6">
-        <v>1.099287486628294</v>
-      </c>
-      <c r="I39" s="6">
-        <v>7663.744349449862</v>
-      </c>
-      <c r="J39" s="6">
-        <v>9380.321964792765</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="8">
-        <v>179.8421110770911</v>
-      </c>
-      <c r="F40" s="9">
-        <v>1335.5017075675992</v>
-      </c>
-      <c r="G40" s="9">
-        <v>156.72455452955484</v>
-      </c>
-      <c r="H40" s="9">
-        <v>79.62527758632659</v>
-      </c>
-      <c r="I40" s="9">
-        <v>7668.02023771236</v>
-      </c>
-      <c r="J40" s="9">
-        <v>9482.918798391343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="5">
-        <v>339.6440762657325</v>
-      </c>
-      <c r="F41" s="6">
-        <v>3249.764161553251</v>
-      </c>
-      <c r="G41" s="6">
-        <v>174.76244378111005</v>
-      </c>
-      <c r="H41" s="6">
-        <v>83.80441819655418</v>
-      </c>
-      <c r="I41" s="6">
-        <v>15176.093084901426</v>
-      </c>
-      <c r="J41" s="6">
-        <v>18624.720937398135</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42" s="8">
-        <v>87.49264670366126</v>
-      </c>
-      <c r="F42" s="9">
-        <v>816.027238793264</v>
-      </c>
-      <c r="G42" s="9">
-        <v>63.761187550122735</v>
-      </c>
-      <c r="H42" s="9">
-        <v>18.92036989823699</v>
-      </c>
-      <c r="I42" s="9">
-        <v>3886.263211448923</v>
-      </c>
-      <c r="J42" s="9">
-        <v>4790.39500189433</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>25</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="B47" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="B48" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="B50" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>32</v>
-      </c>
-      <c r="B53" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="B51" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>30</v>
-      </c>
-      <c r="B56" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>30</v>
-      </c>
-      <c r="B58" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B63" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B67" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>47</v>
-      </c>
-      <c r="B69" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>30</v>
-      </c>
-      <c r="B70" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>50</v>
-      </c>
-      <c r="B72" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>52</v>
-      </c>
-      <c r="B74" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>30</v>
-      </c>
-      <c r="B75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>30</v>
-      </c>
-      <c r="B76" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>30</v>
-      </c>
-      <c r="B77" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>30</v>
-      </c>
-      <c r="B78" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>30</v>
-      </c>
-      <c r="B79" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A30:J30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
